--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_233_Estonia.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_233_Estonia.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R11c5b0d32b564e7a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R0b830087f17348af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Re863baeb7a7d4e60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R8ac143efeced4e26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rfb413bd8a1c74282"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R40bb90f115f04226"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R5ff0e332a9d34c92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R15fbf52275344d54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R87c549f72b2c4311"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R200f4275e6f24c92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R428be2cec8a14a36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R6b566aa07a7e486d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ233CommercialTable" displayName="EEZ233CommercialTable" ref="A1:O9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O9"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ233CommercialTable" displayName="EEZ233CommercialTable" ref="A1:E9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E9"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ233FunctionalTable" displayName="EEZ233FunctionalTable" ref="A1:O14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O14"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ233FunctionalTable" displayName="EEZ233FunctionalTable" ref="A1:E14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E14"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ233ValidationTable" displayName="EEZ233ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ233ValidationTable" displayName="EEZ233ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -3776,7 +3730,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba6ca5ef15a44d08"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re67d79ba8cfb43b9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3786,20 +3740,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -3807,498 +3751,174 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>150.3171743435</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.087849161834222</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1224.1909422225986</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>150.3171743435</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1225.6364005327464</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$47,A2,'Species'!$U$2:$U$47))</x:f>
-        <x:v>184234.20050062065</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.087849161834222</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1224.1909422225986</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>184016.92329180788</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>217.27720881276764</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0011807457973212</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.001180745797321134</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>437.3691173002</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.3954857270398593</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>248.59118641250092</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>437.3691173002</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>270.80615685152907</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$47,A3,'Species'!$U$2:$U$47))</x:f>
-        <x:v>118442.24978161279</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.3954857270398593</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>248.59118641250092</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>108726.107769845</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>9716.142011767792</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0893634676257817</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.08936346762578166</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>75254.6818900792</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.2096466750280204</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>162.04911927941222</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>75254.6818900792</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>176.5514567512808</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$47,A4,'Species'!$U$2:$U$47))</x:f>
-        <x:v>13286323.715047712</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.2096466750280204</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>162.04911927941222</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>12194954.921939667</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1091368.7931080442</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0894934667732628</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.08949346677326271</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>0.000034800000000000006</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.06</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>114.81536214968828</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>0.000034800000000000006</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>114.8153621496883</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$47,A5,'Species'!$U$2:$U$47))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>0.003995574602809153</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.06</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>114.81536214968828</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>0.003995574602809153</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>403.0301932542</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.471945283351211</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>296.44578747189183</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>403.0301932542</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>592.4639294419236</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$47,A6,'Species'!$U$2:$U$47))</x:f>
-        <x:v>238780.8519791212</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.471945283351211</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>296.44578747189183</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>119476.60301419007</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>119304.24896493112</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.9985574242578819</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.9985574242578819</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>979.7962574832999</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.952231977185733</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>895.8431498933078</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>979.7962574832999</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1464.7031430444715</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$47,A7,'Species'!$U$2:$U$47))</x:f>
-        <x:v>1435110.6578789996</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.952231977185733</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>895.8431498933078</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>877743.7655575138</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>557366.8923214858</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.634999545644696</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.634999545644696</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>2287.5454334393003</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.490661148883899</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>309.50035313810383</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>2287.5454334393003</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>356.3635910155166</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$47,A8,'Species'!$U$2:$U$47))</x:f>
-        <x:v>815197.9052715754</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.490661148883899</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>309.50035313810383</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>707996.1194689203</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>107201.78580265515</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.1514157816049457</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.15141578160494581</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>244.5662868076</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.6900145238162887</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>489.7951989837478</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>244.5662868076</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>489.79962243305584</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$47,A9,'Species'!$U$2:$U$47))</x:f>
-        <x:v>119788.47493821692</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.6900145238162887</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>489.7951989837478</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>119787.39311164478</x:v>
       </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>1.0818265721463831</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0000090312222685</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.00000903122226842431</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G9">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O9">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R010448fedb144a01"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R696716286cd641cf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4308,20 +3928,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4329,768 +3939,269 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>185.266479125</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.168310630552163</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1473.365955475521</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>185.266479125</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1603.3889250455195</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$47,A2,'Species'!$U$2:$U$47))</x:f>
-        <x:v>297054.2208112019</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.168310630552163</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1473.365955475521</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>272965.32303359127</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>24088.897777610633</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.08824893033994</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.08824893033994007</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>66.201364602</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.055213272806277</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1135.5683322851276</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>66.201364602</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1147.6503490899308</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$47,A3,'Species'!$U$2:$U$47))</x:f>
-        <x:v>75976.01919571508</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.055213272806277</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1135.5683322851276</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>75176.17319609282</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>799.8459996222664</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0106396211142048</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.010639621114204804</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1.0534374236000001</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.3549052025874895</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2264.1500369980554</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1.0534374236000001</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2281.100011070385</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$47,A4,'Species'!$U$2:$U$47))</x:f>
-        <x:v>2402.9961186359183</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.3549052025874895</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2264.1500369980554</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>2385.1403816190764</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>17.855737016841886</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0074862415455483</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.007486241545548396</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>136.193580338</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.9177233071671473</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>827.4148424786804</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>136.193580338</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>940.505026205097</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$47,A5,'Species'!$U$2:$U$47))</x:f>
-        <x:v>128090.74684475668</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.9177233071671473</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>827.4148424786804</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>112688.58982197377</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>15402.157022782907</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.1366789401403934</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.13667894014039347</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>94.62178222389998</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.1461428860774534</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>140.00478728494866</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>94.62178222389998</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>209.37183973043318</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$47,A6,'Species'!$U$2:$U$47))</x:f>
-        <x:v>19811.136622790338</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.1461428860774534</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>140.00478728494866</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>13247.502492779853</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>6563.634130010485</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.4954620037692232</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.49546200376922317</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1007.5455582827</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.957503851332518</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>906.7840059277147</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1007.5455582827</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1406.7252120967305</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$47,A7,'Species'!$U$2:$U$47))</x:f>
-        <x:v>1417339.73917235</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.957503851332518</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>906.7840059277147</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>913626.1974942625</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>503713.54167808744</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.5513343893373315</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.5513343893373315</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>42904.744574448094</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.386391988924522</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>243.44002778850728</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>42904.744574448094</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>246.037092750079</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$47,A8,'Species'!$U$2:$U$47))</x:f>
-        <x:v>10556158.620281935</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.386391988924522</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>243.44002778850728</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>10444732.211462451</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>111426.4088194836</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0106681920190543</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.010668192019054348</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>0.000034800000000000006</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.06</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>114.81536214968828</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>0.000034800000000000006</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>114.8153621496883</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$47,A9,'Species'!$U$2:$U$47))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>0.003995574602809153</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.06</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>114.81536214968828</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>0.003995574602809153</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>9.3446182052</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.31</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>204.17379446695296</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>9.3446182052</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$47,A10,'Species'!$U$2:$U$47))</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>1907.9261568006516</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.31</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
-        <x:v>1907.9261568006516</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>38.375103333199995</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.319945592068329</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>208.9034402543717</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>38.375103333199995</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>208.90950410210456</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$47,A11,'Species'!$U$2:$U$47))</x:f>
-        <x:v>8016.923807205831</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.319945592068329</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>208.9034402543717</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>8016.691106422485</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>0.23270078334553546</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0000290270362493</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.000029027036249296142</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>34648.3392050645</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.01</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>102.32929922807536</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>34648.3392050645</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>102.32929922807536</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$47,A12,'Species'!$U$2:$U$47))</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>3545540.2702709</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.01</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>102.32929922807536</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
-        <x:v>3545540.2702709</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>229.3049697845</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>229.3049697845</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$47,A13,'Species'!$U$2:$U$47))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>29540.20245258897</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>29540.20245258897</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>436.31567987660003</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.39316931159323</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>247.26879452863113</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>436.31567987660003</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>265.9525179012484</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$47,A14,'Species'!$U$2:$U$47))</x:f>
-        <x:v>116039.25366297686</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.39316931159323</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>247.26879452863113</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>107887.25219702702</x:v>
       </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>8152.001465949841</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0755603771524591</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.07556037715245917</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G14">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O14">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reaa8a9959afb4695"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R096f5522f778449a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5265,7 +4376,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -5364,7 +4475,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>16197878.059393432</x:v>
+        <x:v>14312701.838149164</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5378,7 +4489,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>16197878.059393432</x:v>
+        <x:v>15527713.484062083</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5392,7 +4503,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>1.862645149230957e-9</x:v>
+        <x:v>-1885176.2212442663</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5406,7 +4517,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>1.862645149230957e-9</x:v>
+        <x:v>-670164.5753313471</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5417,9 +4528,9 @@
         <x:v>EEZ_233</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -5431,47 +4542,19 @@
         <x:v>EEZ_233</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_233</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_233</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re50a29d0324c4039"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re25eefe2ca1f4e4a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5518,7 +4601,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
